--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:18</t>
+    <t xml:space="preserve">2026-09-24 01:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -682,13 +682,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="8">
@@ -705,13 +705,13 @@
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -728,13 +728,13 @@
         <v>7</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="10">
@@ -797,13 +797,13 @@
         <v>6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="13">
@@ -823,7 +823,7 @@
         <v>0.04</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.14</v>
@@ -889,13 +889,13 @@
         <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="17">
@@ -915,7 +915,7 @@
         <v>-0.2</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0.08</v>
@@ -958,13 +958,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="20">
@@ -981,13 +981,13 @@
         <v>7</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="21">
@@ -1004,13 +1004,13 @@
         <v>7</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="22">
@@ -1021,7 +1021,7 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>7</v>
@@ -1030,7 +1030,7 @@
         <v>0.23</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0.3</v>
@@ -1050,13 +1050,13 @@
         <v>7</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="24">
@@ -1073,13 +1073,13 @@
         <v>7</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:08</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_miginterna_a_2020_tarapaca.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
